--- a/Measurements/89122254 ASSI vari grip/89122254.xlsx
+++ b/Measurements/89122254 ASSI vari grip/89122254.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoe\Meng\solidworks\Measurements\89122254 ASSI vari grip\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B4BA9B-B414-479B-BF64-2A0A06D072AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880AE724-D374-4BCE-BAC7-088F34DDDD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{32BFC42B-CD3D-49FE-8254-52B3F518DB85}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{32BFC42B-CD3D-49FE-8254-52B3F518DB85}"/>
   </bookViews>
   <sheets>
     <sheet name="FAI" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="Tolerance Table 2" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">FAI!$A$1:$M$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">FAI!$A$1:$M$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Print Page 1'!$A$1:$Q$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Print Page 2'!$A$1:$Q$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Print Page 3'!$A$1:$Q$43</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="33">
   <si>
     <t>Customer</t>
   </si>
@@ -130,10 +130,28 @@
     <t>Meng</t>
   </si>
   <si>
-    <t>1/23/2026</t>
+    <t>Vari Grip</t>
   </si>
   <si>
-    <t>Vari Grip</t>
+    <t>1/26/2026</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Caliper</t>
+  </si>
+  <si>
+    <t>Diameter</t>
+  </si>
+  <si>
+    <t>VMM</t>
+  </si>
+  <si>
+    <t>Angle</t>
+  </si>
+  <si>
+    <t>Height</t>
   </si>
 </sst>
 </file>
@@ -680,10 +698,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>103311</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>100379</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>191234</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>85726</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="256160" cy="264560"/>
     <xdr:sp macro="" textlink="">
@@ -699,7 +717,1016 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10441599" y="1052879"/>
+          <a:off x="1407503" y="3705226"/>
+          <a:ext cx="256160" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>278423</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>159786</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>319314</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>80596</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Straight Arrow Connector 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0758457A-8239-5CB6-1465-AFE4AED7A480}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="11" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1494692" y="3969786"/>
+          <a:ext cx="40891" cy="111310"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>131153</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>98915</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="256160" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C19DAE7-8239-41D3-8F5E-734B8F779CBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3171826" y="3527915"/>
+          <a:ext cx="256160" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>183173</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>172975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>259233</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>73269</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Straight Arrow Connector 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35B80E7E-0427-40A8-B188-9B31A2963336}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="4" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3223846" y="3792475"/>
+          <a:ext cx="76060" cy="281294"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>447554</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>102576</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77666FDF-4CA2-BA4B-7FF4-6735E94B6E01}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8353304" cy="5436576"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>484310</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>5128</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="256160" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D97B8F61-8359-4DBD-8143-F4BC9EE4D04B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="484310" y="2291128"/>
+          <a:ext cx="256160" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>3</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4255</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>79188</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>168519</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{396D0E0C-5F4E-43FF-B7DB-B518217644E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="3" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="612390" y="2555688"/>
+          <a:ext cx="164264" cy="199235"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>57882</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>76931</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="256160" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C174B466-7385-449A-8F30-1EB7757C2621}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="666017" y="1981931"/>
+          <a:ext cx="256160" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>4</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>314042</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>7327</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>161193</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>18711</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6842B695-28CB-4746-A075-607CCE683693}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="6" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="922177" y="2102827"/>
+          <a:ext cx="455285" cy="11384"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>600809</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>102577</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="256160" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C828924E-8EE9-4F84-89CE-712EB6CBABF1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2425213" y="2007577"/>
+          <a:ext cx="256160" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>5</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>468923</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>44357</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>600809</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>131885</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="Straight Arrow Connector 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECF50CAC-F78F-4523-8333-B4BA351FAD6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="13" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2293327" y="2139857"/>
+          <a:ext cx="131886" cy="87528"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>29307</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>52079</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="256160" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="TextBox 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BB0A01E-C686-4C00-B492-A51D7643CFC5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2461845" y="2338079"/>
+          <a:ext cx="256160" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>6</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>344365</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>184359</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>29307</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>80596</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Arrow Connector 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01CFAA6D-EE60-4F99-A588-58970C7F352A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="16" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2168769" y="2470359"/>
+          <a:ext cx="293076" cy="86737"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>29309</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>183173</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="256160" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="TextBox 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F8A23DC-A6F8-4E50-814E-80CAE84B7CE4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2461847" y="2659673"/>
+          <a:ext cx="256160" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>7</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>446942</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>124953</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>29309</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="25" name="Straight Arrow Connector 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31A700DA-50E2-4D96-9C98-092D262E7E10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="24" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2271346" y="2791953"/>
+          <a:ext cx="190501" cy="153470"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>256443</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>102577</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="256160" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="TextBox 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAE761F4-2D30-4F8D-89D0-1C727AD1685E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="256443" y="864577"/>
+          <a:ext cx="256160" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>8</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>512603</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>44357</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>139211</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>65942</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="Straight Arrow Connector 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9C6484A-73B3-4577-B6C1-7552E717DDEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="29" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="512603" y="996857"/>
+          <a:ext cx="234743" cy="21585"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>278142</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>44357</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="256160" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="TextBox 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3D3EC9B-788C-4869-AC38-CB21A361B5D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="278142" y="1187357"/>
           <a:ext cx="256160" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -744,35 +1771,35 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>231391</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>534302</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>174439</xdr:rowOff>
+      <xdr:rowOff>73269</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>417636</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>186104</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>351692</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>176637</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="20" name="Straight Arrow Connector 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0758457A-8239-5CB6-1465-AFE4AED7A480}"/>
+        <xdr:cNvPr id="36" name="Straight Arrow Connector 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEBB7157-8D30-448C-9831-D547956327D5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:cxnSpLocks/>
-          <a:stCxn id="11" idx="2"/>
+          <a:stCxn id="35" idx="3"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10569679" y="1317439"/>
-          <a:ext cx="186245" cy="583165"/>
+        <a:xfrm flipV="1">
+          <a:off x="534302" y="1216269"/>
+          <a:ext cx="425525" cy="103368"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -798,25 +1825,20 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>103311</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>100379</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="256160" cy="264560"/>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>249115</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>183173</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327654" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D97B8F61-8359-4DBD-8143-F4BC9EE4D04B}"/>
+        <xdr:cNvPr id="40" name="TextBox 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A14D965-5D55-4222-B8C0-B5A926E21978}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -824,8 +1846,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10466511" y="1052879"/>
-          <a:ext cx="256160" cy="264560"/>
+          <a:off x="249115" y="564173"/>
+          <a:ext cx="327654" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -860,7 +1882,7 @@
                 </a:schemeClr>
               </a:solidFill>
             </a:rPr>
-            <a:t>9</a:t>
+            <a:t>10</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -869,35 +1891,35 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>231391</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>174439</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>576769</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>146538</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>417636</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>186104</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>124557</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>124953</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="4" name="Straight Arrow Connector 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{396D0E0C-5F4E-43FF-B7DB-B518217644E3}"/>
+        <xdr:cNvPr id="41" name="Straight Arrow Connector 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FAD62DF-FD92-4246-8DCD-DA30F615E071}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:cxnSpLocks/>
-          <a:stCxn id="3" idx="2"/>
+          <a:stCxn id="40" idx="3"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10594591" y="1317439"/>
-          <a:ext cx="186245" cy="583165"/>
+        <a:xfrm flipV="1">
+          <a:off x="576769" y="527538"/>
+          <a:ext cx="155923" cy="168915"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -923,69 +1945,20 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>447554</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>102576</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77666FDF-4CA2-BA4B-7FF4-6735E94B6E01}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="8353304" cy="5436576"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>103311</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>100379</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="256160" cy="264560"/>
+      <xdr:colOff>139211</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161192</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327654" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2533D6E4-A2E2-4B6F-8E58-BA66F2BD3B75}"/>
+        <xdr:cNvPr id="44" name="TextBox 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{076F1378-0D4B-40D9-AA83-66DA4DE7C9AC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -993,8 +1966,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10466511" y="1052879"/>
-          <a:ext cx="256160" cy="264560"/>
+          <a:off x="139211" y="1494692"/>
+          <a:ext cx="327654" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1029,7 +2002,7 @@
                 </a:schemeClr>
               </a:solidFill>
             </a:rPr>
-            <a:t>9</a:t>
+            <a:t>11</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1038,35 +2011,35 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>231391</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>174439</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>466865</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>417636</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>186104</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>51288</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>102972</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BFA7B7C-B1DD-4125-855C-0AF304039C0A}"/>
+        <xdr:cNvPr id="45" name="Straight Arrow Connector 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{645F89D1-F2F4-4640-8B11-4BF1F804E651}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:cxnSpLocks/>
-          <a:stCxn id="2" idx="2"/>
+          <a:stCxn id="44" idx="3"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10594591" y="1317439"/>
-          <a:ext cx="186245" cy="583165"/>
+        <a:xfrm flipV="1">
+          <a:off x="466865" y="1619250"/>
+          <a:ext cx="192558" cy="7722"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1092,69 +2065,20 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>438532</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>105704</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>95251</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91F2324-5593-9F43-89E6-205BBA7DC278}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1" y="1"/>
-          <a:ext cx="4362645" cy="5810250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>103311</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>100379</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="256160" cy="264560"/>
+      <xdr:rowOff>48939</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="338122" cy="264560"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E971DA8-5334-48EF-910A-0F24EF71581C}"/>
+        <xdr:cNvPr id="55" name="TextBox 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AD64B6D-0691-49FD-8B32-12F00DB937C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1162,8 +2086,728 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10466511" y="1052879"/>
-          <a:ext cx="256160" cy="264560"/>
+          <a:off x="1654801" y="48939"/>
+          <a:ext cx="338122" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>14</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>489857</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>122999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>607593</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>103414</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="56" name="Straight Arrow Connector 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D8B9816-ED6E-4B71-94EC-CCEB36EDEAF4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="55" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1706126" y="313499"/>
+          <a:ext cx="117736" cy="170915"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>269803</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>65267</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="334354" cy="244976"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="58" name="TextBox 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAFF7400-BB75-48C4-ADCD-F6FB64034A4A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2098603" y="65267"/>
+          <a:ext cx="334354" cy="244976"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>375557</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>119743</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>436980</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>103414</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="59" name="Straight Arrow Connector 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{521F6B5B-7626-4C1A-AA1E-BAFAF188FC67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="58" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2204357" y="310243"/>
+          <a:ext cx="61423" cy="174171"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>163285</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>87086</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="334946" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="61" name="TextBox 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F77D0414-EE8C-4FF9-B592-25EA943BA2EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2595823" y="277586"/>
+          <a:ext cx="334946" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>13</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>130629</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>161146</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>330758</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>157843</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="62" name="Straight Arrow Connector 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C0A14D7-7538-4D38-9CDD-773E6332AD3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="61" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2563167" y="542146"/>
+          <a:ext cx="200129" cy="187197"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>32658</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>92529</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="326362" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="64" name="TextBox 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{105B868A-7446-4E51-A90C-2389AF47F022}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2465196" y="1426029"/>
+          <a:ext cx="326362" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>15</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>446314</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>34309</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>32658</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>70757</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="65" name="Straight Arrow Connector 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D712A73F-16D2-4B16-972D-36A56CE2B56E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="64" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2270718" y="1558309"/>
+          <a:ext cx="194478" cy="36448"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>527537</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>80597</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="366348" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="80" name="TextBox 79">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D0B9C8F-1807-49A6-83B8-66E0DA6E34A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="527537" y="3319097"/>
+          <a:ext cx="366348" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>16</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>22377</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>432288</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>14654</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="81" name="Straight Arrow Connector 80">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D51679CE-5F70-4C67-9AB8-0681ABD9D5CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="80" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="893885" y="3451377"/>
+          <a:ext cx="146538" cy="182777"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219808</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>65942</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="336756" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="89" name="TextBox 88">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{298D8D52-409F-446E-8525-B84D299FA86D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="219808" y="4066442"/>
+          <a:ext cx="336756" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>17</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>556564</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>7722</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>241788</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>146538</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="90" name="Straight Arrow Connector 89">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97A6CCDF-84D0-4BAF-9A1B-FA6F08261539}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="89" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="556564" y="4198722"/>
+          <a:ext cx="293359" cy="138816"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>476249</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>51288</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327654" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="95" name="TextBox 94">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BC57FC4-D936-4740-80BA-C3F8D920F7E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4125057" y="2908788"/>
+          <a:ext cx="327654" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1198,7 +2842,7 @@
                 </a:schemeClr>
               </a:solidFill>
             </a:rPr>
-            <a:t>9</a:t>
+            <a:t>18</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1207,35 +2851,35 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>231391</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>174439</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>195769</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>139212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>417636</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>186104</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>307731</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>183568</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{116EDCF3-D483-4054-9D18-4AFFD70DD7CE}"/>
+        <xdr:cNvPr id="96" name="Straight Arrow Connector 95">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0848AA34-3E99-4E3B-803F-CFEA86BDC258}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:cxnSpLocks/>
-          <a:stCxn id="2" idx="2"/>
+          <a:stCxn id="95" idx="3"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10594591" y="1317439"/>
-          <a:ext cx="186245" cy="583165"/>
+        <a:xfrm flipV="1">
+          <a:off x="4452711" y="2806212"/>
+          <a:ext cx="111962" cy="234856"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1261,25 +2905,750 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>73270</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>73268</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="329429" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="99" name="TextBox 98">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE76CF43-98AF-4104-861B-5630DB0094AC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6154616" y="1978268"/>
+          <a:ext cx="329429" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>19</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>483576</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>147328</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>237985</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>7327</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="100" name="Straight Arrow Connector 99">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80447191-F8D8-4D82-A025-86BAF6C04732}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="99" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="5956788" y="2242828"/>
+          <a:ext cx="362543" cy="431499"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>102576</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>52079</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327654" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="104" name="TextBox 103">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A15B0EDD-6F75-4CE9-8A83-024261C18DFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5575788" y="3290579"/>
+          <a:ext cx="327654" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>20</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>454269</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>14654</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>102576</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>184359</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="105" name="Straight Arrow Connector 104">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E201ADAF-1222-44B9-8819-C3A2A34C8322}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="104" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="5319346" y="3253154"/>
+          <a:ext cx="256442" cy="169705"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>417633</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>58616</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="337039" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="108" name="TextBox 107">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{886507DE-A14C-4037-B689-CE21982A4478}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7715248" y="1773116"/>
+          <a:ext cx="337039" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>21</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>550347</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>132676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>586153</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>117231</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="109" name="Straight Arrow Connector 108">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DCBD7E6-8A94-4AF6-9FB6-8AE7EC15901F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="108" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7847962" y="2037676"/>
+          <a:ext cx="35806" cy="175055"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>307729</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>36636</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="329714" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="112" name="TextBox 111">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4A0086C2-D52C-493E-9734-D42E1A30983A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7605344" y="3465636"/>
+          <a:ext cx="329714" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>22</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>472586</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>29308</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>542193</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>36636</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="113" name="Straight Arrow Connector 112">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2B90369-6C80-4AC8-A61E-B79CE8B608A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="112" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7770201" y="3267808"/>
+          <a:ext cx="69607" cy="197828"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>527538</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>29308</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="344366" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="117" name="TextBox 116">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C57E4317-E340-46A4-8C85-160E3A1D2FF7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7217019" y="1553308"/>
+          <a:ext cx="344366" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>23</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>586154</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>103368</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>91587</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>80596</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="118" name="Straight Arrow Connector 117">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4F6730C-9259-4D9A-97CA-1E8CB5285812}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="117" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="7275635" y="1817868"/>
+          <a:ext cx="113567" cy="167728"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>446942</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>58616</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327654" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="121" name="TextBox 120">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1DB1D081-247B-4746-A43D-2C94F005B32A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6528288" y="1773116"/>
+          <a:ext cx="327654" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>24</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>468923</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>132676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>2634</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>183173</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="122" name="Straight Arrow Connector 121">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9123ADCB-13DE-4604-9BAC-6DE37C5C8E4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="121" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="6550269" y="2037676"/>
+          <a:ext cx="141846" cy="621997"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>443251</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>95251</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>105703</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97C459F6-94A5-5052-8D67-4C89C94ED892}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E91F2324-5593-9F43-89E6-205BBA7DC278}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1295,6 +3664,415 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="4362645" cy="5810250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>498964</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>115033</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327654" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2533D6E4-A2E2-4B6F-8E58-BA66F2BD3B75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2931502" y="305533"/>
+          <a:ext cx="327654" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>25</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>241789</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>189093</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>54656</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>43962</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BFA7B7C-B1DD-4125-855C-0AF304039C0A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="2" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2674327" y="570093"/>
+          <a:ext cx="421002" cy="235869"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>417635</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>102577</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327654" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16C2E5BB-3A30-4C23-AB94-27F69E5F3B89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3458308" y="1817077"/>
+          <a:ext cx="327654" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>27</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>293077</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>176637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>581462</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>139212</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F64DD864-7F50-4E88-8F77-3503047FCD30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="6" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="3333750" y="2081637"/>
+          <a:ext cx="288385" cy="153075"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>7325</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="351693" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EDDBFA5-C89C-4A10-AB3D-E61C3BDB1322}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3047998" y="952500"/>
+          <a:ext cx="351693" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>28</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>249116</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>132280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>7325</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>7327</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Straight Arrow Connector 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D67C328-066B-4C61-ABCB-1CF19A0A7325}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="9" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2681654" y="1084780"/>
+          <a:ext cx="366344" cy="256047"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>443251</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>95251</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97C459F6-94A5-5052-8D67-4C89C94ED892}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="1" y="1"/>
           <a:ext cx="4092058" cy="5429250"/>
         </a:xfrm>
@@ -1303,6 +4081,486 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>154599</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>129687</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327654" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E971DA8-5334-48EF-910A-0F24EF71581C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2587137" y="320187"/>
+          <a:ext cx="327654" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>29</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>175847</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>13247</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>318426</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Arrow Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{116EDCF3-D483-4054-9D18-4AFFD70DD7CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="2" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2608385" y="584747"/>
+          <a:ext cx="142579" cy="177253"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>505558</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>65942</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327654" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87C205F7-C30E-4E64-83EA-61306D34BCD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="505558" y="1018442"/>
+          <a:ext cx="327654" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>30</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>225077</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>7722</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>43962</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>80596</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="Straight Arrow Connector 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BF7F69C-31F3-49E9-9F67-C9B92163DB2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="6" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="833212" y="1150722"/>
+          <a:ext cx="427019" cy="263374"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>600808</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>87923</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="351408" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="TextBox 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C516690E-5A70-4AF0-8453-CCFCCE70948B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="600808" y="1992923"/>
+          <a:ext cx="351408" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>31</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>344081</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>29703</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>21981</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Straight Arrow Connector 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54C9A5BD-E6DD-46D3-A2C0-20DE80574A8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="11" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="952216" y="2125203"/>
+          <a:ext cx="359303" cy="182778"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>109904</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="327654" cy="264560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="TextBox 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D52AA981-2EAC-4AF1-8CAA-E6A0930EFA0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="798634" y="2776904"/>
+          <a:ext cx="327654" cy="264560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>32</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>518153</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>51684</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>146539</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>153865</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="Straight Arrow Connector 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8AD22C3-88AC-4461-9C22-2F16A7978608}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:cxnSpLocks/>
+          <a:stCxn id="16" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1126288" y="2909184"/>
+          <a:ext cx="236520" cy="102181"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1736,7 +4994,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" style="1" customWidth="1"/>
@@ -1767,7 +5025,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="34" t="s">
         <v>19</v>
@@ -1784,7 +5042,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>15</v>
@@ -1879,109 +5137,197 @@
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="B5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0.8</v>
+      </c>
       <c r="F5" s="3">
         <f>C5+D5</f>
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="G5" s="3">
         <f>C5-E5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
+        <v>0.7</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="2">
+        <v>2.27</v>
+      </c>
+      <c r="J5" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="L5" s="2">
+        <v>2.73</v>
+      </c>
+      <c r="M5" s="2">
+        <v>1.54</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>2</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="B6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.5</v>
+      </c>
       <c r="F6" s="3">
         <f>C6+D6</f>
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="G6" s="3">
         <f>C6-E6</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+        <v>-1.5</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.81</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1.27</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1.22</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1.57</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1.1100000000000001</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="6">
+        <v>15.6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.2</v>
+      </c>
       <c r="F7" s="3">
-        <f t="shared" ref="F7:F19" si="0">C7+D7</f>
-        <v>0</v>
+        <f t="shared" ref="F7:F9" si="0">C7+D7</f>
+        <v>15.799999999999999</v>
       </c>
       <c r="G7" s="3">
-        <f t="shared" ref="G7:G19" si="1">C7-E7</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+        <f t="shared" ref="G7:G9" si="1">C7-E7</f>
+        <v>15.4</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="2">
+        <v>15.65</v>
+      </c>
+      <c r="J7" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="K7" s="2">
+        <v>15.62</v>
+      </c>
+      <c r="L7" s="2">
+        <v>15.65</v>
+      </c>
+      <c r="M7" s="2">
+        <v>15.63</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>4</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="B8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="6">
+        <v>13.6</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.2</v>
+      </c>
       <c r="F8" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>13.799999999999999</v>
       </c>
       <c r="G8" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+        <v>13.4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="2">
+        <v>13.62</v>
+      </c>
+      <c r="J8" s="2">
+        <v>13.61</v>
+      </c>
+      <c r="K8" s="2">
+        <v>13.62</v>
+      </c>
+      <c r="L8" s="2">
+        <v>13.58</v>
+      </c>
+      <c r="M8" s="2">
+        <v>13.62</v>
+      </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>5</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="B9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.1</v>
+      </c>
       <c r="F9" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.8999999999999995</v>
       </c>
       <c r="G9" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="2"/>
@@ -1990,21 +5336,29 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="B10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="6">
+        <v>7.8</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.1</v>
+      </c>
       <c r="F10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="F10:F22" si="2">C10+D10</f>
+        <v>7.8999999999999995</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="G10:G22" si="3">C10-E10</f>
+        <v>7.7</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="2"/>
@@ -2013,21 +5367,29 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>7</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="B11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="6">
+        <v>6.11</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.25</v>
+      </c>
       <c r="F11" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>6.36</v>
       </c>
       <c r="G11" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>5.86</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="2"/>
@@ -2040,198 +5402,1074 @@
       <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="B12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.5</v>
+      </c>
       <c r="F12" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>19.600000000000001</v>
       </c>
       <c r="G12" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+        <f t="shared" si="3"/>
+        <v>18.600000000000001</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="2">
+        <v>19.05</v>
+      </c>
+      <c r="J12" s="2">
+        <v>19.05</v>
+      </c>
+      <c r="K12" s="2">
+        <v>19.04</v>
+      </c>
+      <c r="L12" s="2">
+        <v>19.16</v>
+      </c>
+      <c r="M12" s="2">
+        <v>19.100000000000001</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+      <c r="B13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="6">
+        <v>12</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.5</v>
+      </c>
       <c r="F13" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>12.5</v>
       </c>
       <c r="G13" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+        <f t="shared" si="3"/>
+        <v>11.5</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="2">
+        <v>12.01</v>
+      </c>
+      <c r="J13" s="2">
+        <v>11.78</v>
+      </c>
+      <c r="K13" s="2">
+        <v>11.83</v>
+      </c>
+      <c r="L13" s="2">
+        <v>12.05</v>
+      </c>
+      <c r="M13" s="2">
+        <v>12.15</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+      <c r="B14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="6">
+        <v>5.43</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.125</v>
+      </c>
       <c r="F14" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>5.5549999999999997</v>
       </c>
       <c r="G14" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+        <f t="shared" si="3"/>
+        <v>5.3049999999999997</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="2">
+        <v>5.53</v>
+      </c>
+      <c r="J14" s="2">
+        <v>5.55</v>
+      </c>
+      <c r="K14" s="2">
+        <v>5.54</v>
+      </c>
+      <c r="L14" s="2">
+        <v>5.44</v>
+      </c>
+      <c r="M14" s="2">
+        <v>5.54</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
+      <c r="B15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2.1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.1</v>
+      </c>
       <c r="F15" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="G15" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="J15" s="2">
+        <v>2.19</v>
+      </c>
+      <c r="K15" s="2">
+        <v>2.15</v>
+      </c>
+      <c r="L15" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="M15" s="2">
+        <v>2.16</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="B16" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1.55</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.25</v>
+      </c>
       <c r="F16" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1.8</v>
       </c>
       <c r="G16" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+        <f t="shared" si="3"/>
+        <v>1.3</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1.51</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1.51</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1.55</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1.58</v>
+      </c>
+      <c r="M16" s="2">
+        <v>1.55</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>13</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
+      <c r="B17" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="6">
+        <v>5.78</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.125</v>
+      </c>
       <c r="F17" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>5.9050000000000002</v>
       </c>
       <c r="G17" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+        <f t="shared" si="3"/>
+        <v>5.6550000000000002</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="2">
+        <v>5.71</v>
+      </c>
+      <c r="J17" s="2">
+        <v>5.71</v>
+      </c>
+      <c r="K17" s="2">
+        <v>5.71</v>
+      </c>
+      <c r="L17" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="M17" s="2">
+        <v>5.76</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>14</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
+      <c r="B18" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2</v>
+      </c>
       <c r="F18" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>2.67</v>
       </c>
       <c r="G18" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+        <f t="shared" si="3"/>
+        <v>-1.33</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2">
+        <v>0.99</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1.343</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1.71</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1.0840000000000001</v>
+      </c>
+      <c r="M18" s="2">
+        <v>0.33600000000000002</v>
+      </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>15</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
+      <c r="B19" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2</v>
+      </c>
       <c r="F19" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
+        <v>2.25</v>
+      </c>
+      <c r="G19" s="3">
+        <f t="shared" si="3"/>
+        <v>-1.75</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0.17</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K19" s="2">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="L19" s="2">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="M19" s="2">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="6">
+        <v>11.7</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="2"/>
+        <v>12.2</v>
+      </c>
+      <c r="G20" s="3">
+        <f t="shared" si="3"/>
+        <v>11.2</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20" s="2">
+        <v>11.61</v>
+      </c>
+      <c r="J20" s="2">
+        <v>11.56</v>
+      </c>
+      <c r="K20" s="2">
+        <v>11.63</v>
+      </c>
+      <c r="L20" s="2">
+        <v>11.52</v>
+      </c>
+      <c r="M20" s="2">
+        <v>11.54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1.65</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" si="2"/>
+        <v>1.9</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" si="3"/>
+        <v>1.4</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1.58</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1.75</v>
+      </c>
+      <c r="K21" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="L21" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="M21" s="2">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="6">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="G19" s="3">
-        <f t="shared" si="1"/>
+      <c r="F22" s="3">
+        <f t="shared" si="2"/>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="3"/>
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="2">
+        <v>9.07</v>
+      </c>
+      <c r="J22" s="2">
+        <v>9.11</v>
+      </c>
+      <c r="K22" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="L22" s="2">
+        <v>9.0500000000000007</v>
+      </c>
+      <c r="M22" s="2">
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="6">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E23" s="3">
         <v>0</v>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
+      <c r="F23" s="3">
+        <f>C23+D23</f>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="G23" s="3">
+        <f>C23-E23</f>
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="2">
+        <v>8.93</v>
+      </c>
+      <c r="J23" s="2">
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="K23" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="L23" s="2">
+        <v>8.91</v>
+      </c>
+      <c r="M23" s="2">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2.75</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="F24" s="3">
+        <f>C24+D24</f>
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
+        <f>C24-E24</f>
+        <v>2.5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="2">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="J24" s="2">
+        <v>2.54</v>
+      </c>
+      <c r="K24" s="2">
+        <v>2.64</v>
+      </c>
+      <c r="L24" s="2">
+        <v>2.73</v>
+      </c>
+      <c r="M24" s="2">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F25" s="3">
+        <f>C25+D25</f>
+        <v>2</v>
+      </c>
+      <c r="G25" s="3">
+        <f>C25-E25</f>
+        <v>1</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1.51</v>
+      </c>
+      <c r="J25" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="K25" s="2">
+        <v>1.67</v>
+      </c>
+      <c r="L25" s="2">
+        <v>1.58</v>
+      </c>
+      <c r="M25" s="2">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F26" s="3">
+        <f>C26+D26</f>
+        <v>3</v>
+      </c>
+      <c r="G26" s="3">
+        <f>C26-E26</f>
+        <v>2</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I26" s="2">
+        <v>2.48</v>
+      </c>
+      <c r="J26" s="2">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="K26" s="2">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="L26" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="M26" s="2">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="6">
+        <v>8.6</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" ref="F27:F36" si="4">C27+D27</f>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G27" s="3">
+        <f t="shared" ref="G27:G36" si="5">C27-E27</f>
+        <v>8.5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I27" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="J27" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="K27" s="2">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="L27" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="M27" s="2">
+        <v>8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="6">
+        <v>12.6</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="4"/>
+        <v>12.7</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" si="5"/>
+        <v>12.5</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" s="2">
+        <v>12.56</v>
+      </c>
+      <c r="J28" s="2">
+        <v>12.55</v>
+      </c>
+      <c r="K28" s="2">
+        <v>12.64</v>
+      </c>
+      <c r="L28" s="2">
+        <v>12.55</v>
+      </c>
+      <c r="M28" s="2">
+        <v>12.64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="6">
+        <v>5</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F29" s="3">
+        <f t="shared" si="4"/>
+        <v>5.2</v>
+      </c>
+      <c r="G29" s="3">
+        <f t="shared" si="5"/>
+        <v>4.8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I29" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="J29" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="K29" s="2">
+        <v>4.97</v>
+      </c>
+      <c r="L29" s="2">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="M29" s="2">
+        <v>4.8899999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G30" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>27</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="6">
+        <v>12.7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="4"/>
+        <v>12.799999999999999</v>
+      </c>
+      <c r="G31" s="3">
+        <f t="shared" si="5"/>
+        <v>12.6</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I31" s="2">
+        <v>12.74</v>
+      </c>
+      <c r="J31" s="2">
+        <v>12.73</v>
+      </c>
+      <c r="K31" s="2">
+        <v>12.73</v>
+      </c>
+      <c r="L31" s="2">
+        <v>12.72</v>
+      </c>
+      <c r="M31" s="2">
+        <v>12.73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>28</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="6">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="4"/>
+        <v>8.7999999999999989</v>
+      </c>
+      <c r="G32" s="3">
+        <f t="shared" si="5"/>
+        <v>8.6</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I32" s="2">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="J32" s="2">
+        <v>8.73</v>
+      </c>
+      <c r="K32" s="2">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="L32" s="2">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="M32" s="2">
+        <v>8.7200000000000006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>29</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="6">
+        <v>9.9</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="G33" s="3">
+        <f t="shared" si="5"/>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I33" s="2">
+        <v>9.8800000000000008</v>
+      </c>
+      <c r="J33" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="K33" s="2">
+        <v>9.94</v>
+      </c>
+      <c r="L33" s="2">
+        <v>9.94</v>
+      </c>
+      <c r="M33" s="2">
+        <v>9.8699999999999992</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>30</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="6">
+        <v>4.25</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="F34" s="3">
+        <f t="shared" si="4"/>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="G34" s="3">
+        <f t="shared" si="5"/>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I34" s="2">
+        <v>4.26</v>
+      </c>
+      <c r="J34" s="2">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="K34" s="2">
+        <v>4.29</v>
+      </c>
+      <c r="L34" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="M34" s="2">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>31</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="6">
+        <v>25</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F35" s="3">
+        <f t="shared" si="4"/>
+        <v>25.5</v>
+      </c>
+      <c r="G35" s="3">
+        <f t="shared" si="5"/>
+        <v>24.5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" s="2">
+        <f>28.99-I34</f>
+        <v>24.729999999999997</v>
+      </c>
+      <c r="J35" s="2">
+        <f>28.93-J34</f>
+        <v>24.7</v>
+      </c>
+      <c r="K35" s="2">
+        <f>28.97-K34</f>
+        <v>24.68</v>
+      </c>
+      <c r="L35" s="2">
+        <f>29-L34</f>
+        <v>24.7</v>
+      </c>
+      <c r="M35" s="2">
+        <f>29.22-M34</f>
+        <v>24.93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>32</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="6">
+        <v>4.4749999999999996</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0.125</v>
+      </c>
+      <c r="F36" s="3">
+        <f t="shared" si="4"/>
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G36" s="3">
+        <f t="shared" si="5"/>
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="2">
+        <v>4.46</v>
+      </c>
+      <c r="J36" s="2">
+        <v>4.57</v>
+      </c>
+      <c r="K36" s="2">
+        <v>4.58</v>
+      </c>
+      <c r="L36" s="2">
+        <v>4.47</v>
+      </c>
+      <c r="M36" s="2">
+        <v>4.59</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G1:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:M19">
+  <conditionalFormatting sqref="I5:M36">
     <cfRule type="cellIs" dxfId="0" priority="22" operator="notBetween">
       <formula>$G5</formula>
       <formula>$F5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="80" orientation="landscape" r:id="rId1"/>
+  <pageSetup scale="68" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
